--- a/packages/search-pages/content/downloads/files/gst-invoice-format/gst-invoice-format.xlsx
+++ b/packages/search-pages/content/downloads/files/gst-invoice-format/gst-invoice-format.xlsx
@@ -172,25 +172,25 @@
   <fonts count="4">
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF6B7280"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -264,8 +264,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <cols>
-    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
@@ -762,7 +765,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" fitToHeight="0"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="1"/>
   <headerFooter>
     <oddFooter>&amp;CMade with Saroh · saroh.in</oddFooter>
   </headerFooter>
@@ -771,8 +774,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <cols>
-    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
@@ -1325,7 +1331,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" fitToHeight="0"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="1"/>
   <headerFooter>
     <oddFooter>&amp;CMade with Saroh · saroh.in</oddFooter>
   </headerFooter>
